--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260717.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260717.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.90%</t>
+          <t>11.15%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.08%</t>
+          <t>10.19%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.63%</t>
+          <t>8.51%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.29%</t>
+          <t>7.27%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>5.64%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.22%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.49%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.43%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1100,51 +1100,51 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>30,982</t>
+          <t>22,651</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>22,651</t>
+          <t>30,982</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1166,46 +1166,46 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>28,056</t>
+          <t>21,075</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>21,075</t>
+          <t>28,056</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>30,850</t>
+          <t>13,486</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>13,486</t>
+          <t>30,850</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1364,24 +1364,24 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>31,233</t>
+          <t>10,834</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>10,834</t>
+          <t>31,233</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1481,44 +1481,44 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,661</t>
+          <t>16,412</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>16,412</t>
+          <t>13,661</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1562,24 +1562,24 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>96,170</t>
+          <t>5,981</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,22 +1591,22 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>5,981</t>
+          <t>96,170</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>113,436,105</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
